--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20231.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20231.xlsx
@@ -770,10 +770,10 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -782,7 +782,7 @@
         <v>6</v>
       </c>
       <c r="G6">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="H6">
         <v>6.3</v>
@@ -927,10 +927,10 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6">
         <v>12</v>
@@ -1093,10 +1093,10 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -1105,7 +1105,7 @@
         <v>6</v>
       </c>
       <c r="G6">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="H6">
         <v>6.3</v>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20231.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="85">
   <si>
     <t>Mat</t>
   </si>
@@ -82,124 +82,127 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>GARZA</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
     <t>TENTZOHUA</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
     <t>BARRAGAN</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
   </si>
   <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>QUIÑONES</t>
-  </si>
-  <si>
-    <t>LEÓN</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>CORONADO</t>
+    <t>LEON</t>
   </si>
   <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>MIXCOHA</t>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>NEGRETE</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>GALICIA</t>
   </si>
   <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
+    <t>JENNYFER ARIANA</t>
   </si>
   <si>
     <t>ABIGAIL</t>
@@ -208,67 +211,67 @@
     <t>MIROSLAVA</t>
   </si>
   <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
     <t>ANGEL DAVID</t>
   </si>
   <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
     <t>RUBI</t>
   </si>
   <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
     <t>KAREN ITZEL</t>
   </si>
   <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERMIN</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
     <t>ALESSANDRA</t>
   </si>
   <si>
-    <t>CRISTHIAN ALFONSO</t>
+    <t>YAZURI</t>
+  </si>
+  <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>RONALDO</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
+  </si>
+  <si>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>FATIMA MARILYN</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>ITZEL ABIGAIL</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>LUIS REY</t>
+  </si>
+  <si>
+    <t>ALONDRA YURIDIA</t>
+  </si>
+  <si>
+    <t>CITLALI ESPERANZA</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
+  </si>
+  <si>
+    <t>NATALIE</t>
   </si>
   <si>
     <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>AMY JULIET</t>
-  </si>
-  <si>
-    <t>MARIA TERESA</t>
-  </si>
-  <si>
-    <t>REGINA ISABEL</t>
-  </si>
-  <si>
-    <t>FATIMA MARILYN</t>
-  </si>
-  <si>
-    <t>ITZEL ABIGAIL</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
-    <t>CITLALI ESPERANZA</t>
-  </si>
-  <si>
-    <t>ALMA KAREN</t>
-  </si>
-  <si>
-    <t>YAZURI</t>
   </si>
 </sst>
 </file>
@@ -838,16 +841,19 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>40.54</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -861,16 +867,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>51.52</v>
+      </c>
+      <c r="H3">
+        <v>6.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -884,16 +893,19 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H4">
+        <v>6.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -907,16 +919,19 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>88.45999999999999</v>
+      </c>
+      <c r="H5">
+        <v>7.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -930,16 +945,19 @@
         <v>12</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H6">
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -995,16 +1013,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>45.95</v>
+        <v>40.54</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1021,16 +1039,16 @@
         <v>0</v>
       </c>
       <c r="E3">
+        <v>16</v>
+      </c>
+      <c r="F3">
         <v>17</v>
       </c>
-      <c r="F3">
-        <v>16</v>
-      </c>
       <c r="G3">
-        <v>48.48</v>
+        <v>51.52</v>
       </c>
       <c r="H3">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1047,16 +1065,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>62.5</v>
+        <v>75</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1082,7 +1100,7 @@
         <v>88.45999999999999</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1099,16 +1117,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="H6">
-        <v>6.3</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1118,7 +1136,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1150,7 +1168,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920071</v>
+        <v>23330051920356</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
@@ -1162,10 +1180,10 @@
         <v>61</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1173,7 +1191,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920078</v>
+        <v>21330051920071</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
@@ -1196,7 +1214,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920102</v>
+        <v>21330051920078</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -1219,7 +1237,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920104</v>
+        <v>21330051920080</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -1242,7 +1260,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920107</v>
+        <v>21330051920102</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -1265,7 +1283,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920109</v>
+        <v>21330051920107</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -1294,7 +1312,7 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
         <v>67</v>
@@ -1311,7 +1329,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920118</v>
+        <v>21330051920031</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
@@ -1326,7 +1344,7 @@
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1334,10 +1352,10 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920121</v>
+        <v>21330051920063</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
         <v>48</v>
@@ -1349,7 +1367,7 @@
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1357,10 +1375,10 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920123</v>
+        <v>21330051920141</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
         <v>49</v>
@@ -1372,7 +1390,7 @@
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1380,7 +1398,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920031</v>
+        <v>21330051920147</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
@@ -1395,7 +1413,7 @@
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1403,10 +1421,10 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920139</v>
+        <v>23330051920320</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
         <v>51</v>
@@ -1415,21 +1433,21 @@
         <v>72</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920148</v>
+        <v>21330051920260</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
         <v>52</v>
@@ -1441,18 +1459,18 @@
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920300</v>
+        <v>21330051920305</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
         <v>53</v>
@@ -1472,10 +1490,10 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920260</v>
+        <v>21330051920089</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
         <v>54</v>
@@ -1495,10 +1513,10 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920083</v>
+        <v>21330051920092</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
         <v>55</v>
@@ -1518,13 +1536,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920089</v>
+        <v>21330051920093</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="D18" t="s">
         <v>77</v>
@@ -1541,13 +1559,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920093</v>
+        <v>21330051920097</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
         <v>78</v>
@@ -1564,10 +1582,10 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920097</v>
+        <v>21330051920099</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
         <v>57</v>
@@ -1616,7 +1634,7 @@
         <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D22" t="s">
         <v>81</v>
@@ -1656,13 +1674,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920063</v>
+        <v>21330051920120</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D24" t="s">
         <v>83</v>
@@ -1671,9 +1689,32 @@
         <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>21330051920148</v>
+      </c>
+      <c r="B25" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20231.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="79">
   <si>
     <t>Mat</t>
   </si>
@@ -82,105 +82,96 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>GARZA</t>
   </si>
   <si>
-    <t>ANTONIO</t>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
+    <t>NEGRETE</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
   </si>
   <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>NEGRETE</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -202,46 +193,37 @@
     <t>GALICIA</t>
   </si>
   <si>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>RUBI</t>
+  </si>
+  <si>
+    <t>KAREN ITZEL</t>
+  </si>
+  <si>
+    <t>ALESSANDRA</t>
+  </si>
+  <si>
+    <t>YAZURI</t>
+  </si>
+  <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
     <t>JENNYFER ARIANA</t>
   </si>
   <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
   </si>
   <si>
     <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>RUBI</t>
-  </si>
-  <si>
-    <t>KAREN ITZEL</t>
-  </si>
-  <si>
-    <t>ALESSANDRA</t>
-  </si>
-  <si>
-    <t>YAZURI</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>RONALDO</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>MARIA TERESA</t>
-  </si>
-  <si>
-    <t>MARIA MICHELLE</t>
   </si>
   <si>
     <t>FATIMA MARILYN</t>
@@ -1136,7 +1118,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1168,22 +1150,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920356</v>
+        <v>21330051920305</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1191,16 +1173,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920071</v>
+        <v>21330051920102</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1214,16 +1196,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920078</v>
+        <v>21330051920107</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1237,22 +1219,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920080</v>
+        <v>21330051920111</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1260,22 +1242,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920102</v>
+        <v>21330051920031</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1283,22 +1265,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920107</v>
+        <v>21330051920063</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1306,22 +1288,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920111</v>
+        <v>21330051920141</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1329,7 +1311,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920031</v>
+        <v>23330051920356</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
@@ -1338,21 +1320,21 @@
         <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920063</v>
+        <v>23330051920320</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
@@ -1361,82 +1343,82 @@
         <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920141</v>
+        <v>21330051920260</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
         <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920147</v>
+        <v>21330051920080</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
         <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920320</v>
+        <v>21330051920089</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
         <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1444,16 +1426,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920260</v>
+        <v>21330051920092</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
         <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1467,16 +1449,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920305</v>
+        <v>21330051920093</v>
       </c>
       <c r="B15" t="s">
         <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1490,16 +1472,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920089</v>
+        <v>21330051920097</v>
       </c>
       <c r="B16" t="s">
         <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -1513,16 +1495,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920092</v>
+        <v>21330051920099</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -1536,16 +1518,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920093</v>
+        <v>21330051920100</v>
       </c>
       <c r="B18" t="s">
         <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -1559,16 +1541,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920097</v>
+        <v>21330051920101</v>
       </c>
       <c r="B19" t="s">
         <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -1582,16 +1564,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920099</v>
+        <v>21330051920103</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -1605,22 +1587,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920100</v>
+        <v>21330051920120</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1628,93 +1610,24 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920101</v>
+        <v>21330051920148</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920103</v>
-      </c>
-      <c r="B23" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" t="s">
-        <v>82</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920120</v>
-      </c>
-      <c r="B24" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" t="s">
-        <v>57</v>
-      </c>
-      <c r="D24" t="s">
-        <v>83</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920148</v>
-      </c>
-      <c r="B25" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" t="s">
-        <v>60</v>
-      </c>
-      <c r="D25" t="s">
-        <v>84</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20231.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20231.xlsx
@@ -755,10 +755,10 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -767,7 +767,7 @@
         <v>6</v>
       </c>
       <c r="G6">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="H6">
         <v>6.3</v>
@@ -924,10 +924,10 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -936,7 +936,7 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="H6">
         <v>6.3</v>
@@ -1093,10 +1093,10 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -1105,7 +1105,7 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="H6">
         <v>7</v>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20231.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="42">
   <si>
     <t>Mat</t>
   </si>
@@ -82,178 +82,67 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>TETLA</t>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>GARZA</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>GARZA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>NEGRETE</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>MARIA MICHELLE</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>RUBI</t>
-  </si>
-  <si>
-    <t>KAREN ITZEL</t>
-  </si>
-  <si>
-    <t>ALESSANDRA</t>
-  </si>
-  <si>
-    <t>YAZURI</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>VANESSA AMAIRANY</t>
+  </si>
+  <si>
+    <t>MILKA SARAY</t>
+  </si>
+  <si>
+    <t>RONALDO</t>
   </si>
   <si>
     <t>JENNYFER ARIANA</t>
   </si>
   <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>MARIA TERESA</t>
+    <t>EVELYN JOHANA</t>
   </si>
   <si>
     <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>FATIMA MARILYN</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>ITZEL ABIGAIL</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>LUIS REY</t>
-  </si>
-  <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
-    <t>CITLALI ESPERANZA</t>
-  </si>
-  <si>
-    <t>ALMA KAREN</t>
-  </si>
-  <si>
-    <t>NATALIE</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
   </si>
 </sst>
 </file>
@@ -758,10 +647,10 @@
         <v>13</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6">
         <v>6</v>
@@ -770,7 +659,7 @@
         <v>46.15</v>
       </c>
       <c r="H6">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
     </row>
   </sheetData>
@@ -927,10 +816,10 @@
         <v>13</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6">
         <v>9</v>
@@ -939,7 +828,7 @@
         <v>69.23</v>
       </c>
       <c r="H6">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
     </row>
   </sheetData>
@@ -995,16 +884,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>40.54</v>
+        <v>51.35</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1021,16 +910,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>51.52</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H3">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1047,16 +936,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1073,13 +962,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>88.45999999999999</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H5">
         <v>7.5</v>
@@ -1096,19 +985,19 @@
         <v>13</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>69.23</v>
+        <v>84.62</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -1118,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1150,16 +1039,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920305</v>
+        <v>21330051920071</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1173,16 +1062,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920102</v>
+        <v>21330051920082</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1196,22 +1085,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920107</v>
+        <v>21330051920140</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1219,22 +1108,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920111</v>
+        <v>21330051920147</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1242,392 +1131,70 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920031</v>
+        <v>23330051920356</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920063</v>
+        <v>21330051920075</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920141</v>
+        <v>21330051920080</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920356</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920320</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920260</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" t="s">
-        <v>67</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920080</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920089</v>
-      </c>
-      <c r="B13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920092</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" t="s">
-        <v>70</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920093</v>
-      </c>
-      <c r="B15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" t="s">
-        <v>71</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920097</v>
-      </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" t="s">
-        <v>72</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920099</v>
-      </c>
-      <c r="B17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" t="s">
-        <v>73</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920100</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920101</v>
-      </c>
-      <c r="B19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920103</v>
-      </c>
-      <c r="B20" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" t="s">
-        <v>76</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920120</v>
-      </c>
-      <c r="B21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" t="s">
-        <v>77</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920148</v>
-      </c>
-      <c r="B22" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" t="s">
-        <v>57</v>
-      </c>
-      <c r="D22" t="s">
-        <v>78</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20231.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="45">
   <si>
     <t>Mat</t>
   </si>
@@ -82,67 +82,76 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CASANOVA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>GARZA</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>DE JESUS</t>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>GARZA</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>BRETON</t>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
+    <t>LUCIA</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>RONALDO</t>
+  </si>
+  <si>
+    <t>JENNYFER ARIANA</t>
   </si>
   <si>
     <t>ABIGAIL</t>
   </si>
   <si>
-    <t>VANESSA AMAIRANY</t>
+    <t>EVELYN JOHANA</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
   </si>
   <si>
     <t>MILKA SARAY</t>
-  </si>
-  <si>
-    <t>RONALDO</t>
-  </si>
-  <si>
-    <t>JENNYFER ARIANA</t>
-  </si>
-  <si>
-    <t>EVELYN JOHANA</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
   </si>
 </sst>
 </file>
@@ -1007,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1039,22 +1048,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920071</v>
+        <v>23330051920347</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1062,16 +1071,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920082</v>
+        <v>21330051920078</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1085,16 +1094,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920140</v>
+        <v>21330051920147</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1108,45 +1117,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920147</v>
+        <v>23330051920356</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920356</v>
+        <v>21330051920071</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1160,10 +1169,10 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1183,10 +1192,10 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1195,6 +1204,29 @@
         <v>11</v>
       </c>
       <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920140</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20231.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="42">
   <si>
     <t>Mat</t>
   </si>
@@ -85,9 +85,6 @@
     <t>CASANOVA</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
@@ -109,9 +106,6 @@
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>GOMEZ</t>
   </si>
   <si>
@@ -131,9 +125,6 @@
   </si>
   <si>
     <t>LUCIA</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
   </si>
   <si>
     <t>RONALDO</t>
@@ -1016,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1054,10 +1045,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1071,22 +1062,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920078</v>
+        <v>21330051920147</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1094,45 +1085,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920147</v>
+        <v>23330051920356</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920356</v>
+        <v>21330051920071</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1140,16 +1131,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920071</v>
+        <v>21330051920075</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1163,16 +1154,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920075</v>
+        <v>21330051920080</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1186,47 +1177,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920080</v>
+        <v>21330051920140</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920140</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20231.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20231.xlsx
@@ -893,7 +893,7 @@
         <v>51.35</v>
       </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -919,7 +919,7 @@
         <v>84.84999999999999</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -945,7 +945,7 @@
         <v>87.5</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -971,7 +971,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -997,7 +997,7 @@
         <v>84.62</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20231.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20231.xlsx
@@ -893,7 +893,7 @@
         <v>51.35</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -919,7 +919,7 @@
         <v>84.84999999999999</v>
       </c>
       <c r="H3">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -945,7 +945,7 @@
         <v>87.5</v>
       </c>
       <c r="H4">
-        <v>9.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -971,7 +971,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="H5">
-        <v>9.800000000000001</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -997,7 +997,7 @@
         <v>84.62</v>
       </c>
       <c r="H6">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
